--- a/output/graficos_nacionales/plot_nacional_d_piramide_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_piramide_a_2019.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 15:39</t>
+    <t xml:space="preserve">2026-10-05 21:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
